--- a/data/trans_orig/P57GLOBAL_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304841</t>
+          <t>302186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>343880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187465</t>
+          <t>188598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220654</t>
+          <t>222033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>503834</t>
+          <t>501166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>554212</t>
+          <t>556156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126509</t>
+          <t>127061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166100</t>
+          <t>168755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84875</t>
+          <t>83496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118064</t>
+          <t>116931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222258</t>
+          <t>220314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272636</t>
+          <t>275304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>216596</t>
+          <t>217030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255759</t>
+          <t>254214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>234619</t>
+          <t>235010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>269667</t>
+          <t>270413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461105</t>
+          <t>461117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>512306</t>
+          <t>515432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109625</t>
+          <t>111170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148788</t>
+          <t>148354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102198</t>
+          <t>101452</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137246</t>
+          <t>136855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224943</t>
+          <t>221817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>276144</t>
+          <t>276132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>384002</t>
+          <t>383806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427043</t>
+          <t>424691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107434</t>
+          <t>107653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130102</t>
+          <t>130234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>501357</t>
+          <t>500671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>547307</t>
+          <t>545941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114502</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157543</t>
+          <t>157739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59368</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161040</t>
+          <t>162406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>206990</t>
+          <t>207676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>871915</t>
+          <t>869866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>933639</t>
+          <t>931486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>505815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>556318</t>
+          <t>554093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1391052</t>
+          <t>1397961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1472344</t>
+          <t>1474442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304695</t>
+          <t>306848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366419</t>
+          <t>368468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157967</t>
+          <t>160192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204773</t>
+          <t>208470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>480276</t>
+          <t>478178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561568</t>
+          <t>554659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>234040</t>
+          <t>234437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267849</t>
+          <t>267949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>431775</t>
+          <t>431794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>469219</t>
+          <t>468255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>676737</t>
+          <t>676528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>728863</t>
+          <t>729652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82706</t>
+          <t>82606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116515</t>
+          <t>116118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98538</t>
+          <t>99502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135982</t>
+          <t>135963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189449</t>
+          <t>188660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241575</t>
+          <t>241784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162861</t>
+          <t>161586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>193594</t>
+          <t>195527</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>846174</t>
+          <t>847938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>910999</t>
+          <t>910027</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1020756</t>
+          <t>1019977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1091822</t>
+          <t>1096488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103769</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134502</t>
+          <t>135777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337761</t>
+          <t>338733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>402586</t>
+          <t>400822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454301</t>
+          <t>449635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525367</t>
+          <t>526146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2242634</t>
+          <t>2242352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2350022</t>
+          <t>2352920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2384857</t>
+          <t>2387928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2491844</t>
+          <t>2491068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4662927</t>
+          <t>4661021</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4812851</t>
+          <t>4807410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>914101</t>
+          <t>911203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1021489</t>
+          <t>1021771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>883154</t>
+          <t>883930</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>990141</t>
+          <t>987070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1826270</t>
+          <t>1831711</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1976194</t>
+          <t>1978100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>273692</t>
+          <t>272711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>313571</t>
+          <t>313118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200417</t>
+          <t>199919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235051</t>
+          <t>234814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>485419</t>
+          <t>485034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>540946</t>
+          <t>540019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,45%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121713</t>
+          <t>122166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161592</t>
+          <t>162573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75025</t>
+          <t>75262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109659</t>
+          <t>110157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204414</t>
+          <t>205341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259941</t>
+          <t>260326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260713</t>
+          <t>261289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301532</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>227809</t>
+          <t>227255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>261706</t>
+          <t>262791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501061</t>
+          <t>502275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>552658</t>
+          <t>555973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114046</t>
+          <t>114438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154865</t>
+          <t>154289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72642</t>
+          <t>71557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106539</t>
+          <t>107093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197269</t>
+          <t>193954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248866</t>
+          <t>247652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>400123</t>
+          <t>399021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>447510</t>
+          <t>447667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172541</t>
+          <t>173701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202221</t>
+          <t>202709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>584804</t>
+          <t>585348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>639542</t>
+          <t>639037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174419</t>
+          <t>174262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221806</t>
+          <t>222908</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86652</t>
+          <t>85492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241580</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296318</t>
+          <t>295774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>770179</t>
+          <t>768666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>836653</t>
+          <t>834519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>580082</t>
+          <t>584090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>628526</t>
+          <t>627652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1365557</t>
+          <t>1374194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1443468</t>
+          <t>1448636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306648</t>
+          <t>308782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373122</t>
+          <t>374635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132199</t>
+          <t>133073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180643</t>
+          <t>176635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>460558</t>
+          <t>455390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538469</t>
+          <t>529832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>343381</t>
+          <t>342785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382954</t>
+          <t>383055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>556036</t>
+          <t>555088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>603645</t>
+          <t>602690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>913570</t>
+          <t>912990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>974645</t>
+          <t>974894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117446</t>
+          <t>117345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157019</t>
+          <t>157615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148583</t>
+          <t>149538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196192</t>
+          <t>197140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277983</t>
+          <t>277734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339058</t>
+          <t>339638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145507</t>
+          <t>145858</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177387</t>
+          <t>177175</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>774834</t>
+          <t>777702</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>831657</t>
+          <t>832763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>933244</t>
+          <t>935052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>999348</t>
+          <t>1001783</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87604</t>
+          <t>87816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119484</t>
+          <t>119133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267462</t>
+          <t>266356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324285</t>
+          <t>321417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>364761</t>
+          <t>362326</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>429057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2266449</t>
+          <t>2273941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2387355</t>
+          <t>2387889</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2598414</t>
+          <t>2596197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2705402</t>
+          <t>2700480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4903252</t>
+          <t>4902803</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5053569</t>
+          <t>5056820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>994128</t>
+          <t>993594</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1115034</t>
+          <t>1107542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>810288</t>
+          <t>815210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>917276</t>
+          <t>919493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1843603</t>
+          <t>1840352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1993920</t>
+          <t>1994369</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016 (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>320548</t>
+          <t>321259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353949</t>
+          <t>356903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,82 +6018,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>275053</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>260348</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>289459</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>80,56%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>614033</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>590017</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>636139</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>82,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>275053</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>259636</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>288770</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>84,57%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>614033</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>589883</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>636664</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>79,78%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74278</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107679</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,82 +6131,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>66392</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51986</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>81097</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>155639</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>133533</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>179655</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>17,35%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66392</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52675</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81809</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>155639</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>133008</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>179789</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271266</t>
+          <t>270213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303476</t>
+          <t>303873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>275769</t>
+          <t>276015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308132</t>
+          <t>308232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>557419</t>
+          <t>559836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>604267</t>
+          <t>605097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69622</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101832</t>
+          <t>102885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58587</t>
+          <t>58487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90950</t>
+          <t>90704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135550</t>
+          <t>134720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182398</t>
+          <t>179981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>432807</t>
+          <t>434083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>465084</t>
+          <t>466674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132878</t>
+          <t>132042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150422</t>
+          <t>150284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>576881</t>
+          <t>573742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>610044</t>
+          <t>609639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>86865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73488</t>
+          <t>73893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106651</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>908337</t>
+          <t>906114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>959908</t>
+          <t>956882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>682805</t>
+          <t>681973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>721743</t>
+          <t>722480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1602537</t>
+          <t>1600038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1668526</t>
+          <t>1666387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176609</t>
+          <t>179635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228180</t>
+          <t>230403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97529</t>
+          <t>96792</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136467</t>
+          <t>137299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287263</t>
+          <t>289402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353252</t>
+          <t>355751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>491523</t>
+          <t>492302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>530939</t>
+          <t>530005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>617599</t>
+          <t>618802</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>654489</t>
+          <t>655283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1126402</t>
+          <t>1123581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1175545</t>
+          <t>1175800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83442</t>
+          <t>84376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122858</t>
+          <t>122079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>76064</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>112545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170183</t>
+          <t>169928</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219326</t>
+          <t>222147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211527</t>
+          <t>210466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>239486</t>
+          <t>238591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>887293</t>
+          <t>884547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>933951</t>
+          <t>931765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1108102</t>
+          <t>1110703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1164146</t>
+          <t>1163815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46708</t>
+          <t>47603</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74667</t>
+          <t>75728</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>140499</t>
+          <t>142685</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187157</t>
+          <t>189903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196498</t>
+          <t>196829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>252542</t>
+          <t>249941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2704659</t>
+          <t>2702866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2795957</t>
+          <t>2793247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2923447</t>
+          <t>2915562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3003523</t>
+          <t>3004084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5651885</t>
+          <t>5651621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5778685</t>
+          <t>5775713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563407</t>
+          <t>566117</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654705</t>
+          <t>656498</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>492295</t>
+          <t>491734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>572371</t>
+          <t>580256</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1076497</t>
+          <t>1079469</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1203297</t>
+          <t>1203561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023 (tasa de respuesta: 98,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266582</t>
+          <t>266824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311429</t>
+          <t>312572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>220761</t>
+          <t>221106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257005</t>
+          <t>256406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>498818</t>
+          <t>496873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>555744</t>
+          <t>556838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184853</t>
+          <t>183710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229700</t>
+          <t>229458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186398</t>
+          <t>186997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222642</t>
+          <t>222297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383941</t>
+          <t>382847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440867</t>
+          <t>442812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>265294</t>
+          <t>265104</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>308976</t>
+          <t>307439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226381</t>
+          <t>225881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>260048</t>
+          <t>259355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501954</t>
+          <t>501882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>555518</t>
+          <t>557149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138348</t>
+          <t>139885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182030</t>
+          <t>182220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117174</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150841</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269028</t>
+          <t>267397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322592</t>
+          <t>322664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110260</t>
+          <t>106364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>439104</t>
+          <t>437978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101433</t>
+          <t>101176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120567</t>
+          <t>119753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170261</t>
+          <t>155507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>555366</t>
+          <t>556159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>222481</t>
+          <t>223607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>551325</t>
+          <t>555221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62572</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270224</t>
+          <t>269431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655329</t>
+          <t>670083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>634948</t>
+          <t>636498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>703029</t>
+          <t>704632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>457497</t>
+          <t>456363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>502632</t>
+          <t>502582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1108349</t>
+          <t>1110272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1190147</t>
+          <t>1188960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>321251</t>
+          <t>319648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>389332</t>
+          <t>387782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256229</t>
+          <t>256279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301364</t>
+          <t>302498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>592993</t>
+          <t>594180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>674791</t>
+          <t>672868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301616</t>
+          <t>300755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>343537</t>
+          <t>342785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>377033</t>
+          <t>398388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>585954</t>
+          <t>583917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>683227</t>
+          <t>674833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>911682</t>
+          <t>906582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121151</t>
+          <t>121903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163072</t>
+          <t>163933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238977</t>
+          <t>241014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>447898</t>
+          <t>426543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377937</t>
+          <t>383037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>606392</t>
+          <t>614786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82465</t>
+          <t>82477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133970</t>
+          <t>133873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>453101</t>
+          <t>450015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>503477</t>
+          <t>501633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>548695</t>
+          <t>545151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>624158</t>
+          <t>623968</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103897</t>
+          <t>103994</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155402</t>
+          <t>155390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237932</t>
+          <t>239776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>288308</t>
+          <t>291394</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>355118</t>
+          <t>355308</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430581</t>
+          <t>434125</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1479551</t>
+          <t>1386556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2123840</t>
+          <t>2120645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1897948</t>
+          <t>1890062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2145835</t>
+          <t>2140009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3424810</t>
+          <t>3416545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4215593</t>
+          <t>4208066</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1208185</t>
+          <t>1211380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1852474</t>
+          <t>1945469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1163995</t>
+          <t>1169821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1411882</t>
+          <t>1419768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2426262</t>
+          <t>2433789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3217045</t>
+          <t>3225310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57GLOBAL_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302186</t>
+          <t>302945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>343880</t>
+          <t>345365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>186620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222033</t>
+          <t>219883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>501166</t>
+          <t>501939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>556156</t>
+          <t>553048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>125576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168755</t>
+          <t>167996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83496</t>
+          <t>85646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>118909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220314</t>
+          <t>223422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275304</t>
+          <t>274531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>217030</t>
+          <t>213414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254214</t>
+          <t>255123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>235010</t>
+          <t>234167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270413</t>
+          <t>269960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461117</t>
+          <t>462749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>515432</t>
+          <t>515692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111170</t>
+          <t>110261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148354</t>
+          <t>151970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101452</t>
+          <t>101905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136855</t>
+          <t>137698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>221817</t>
+          <t>221557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>276132</t>
+          <t>274500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>383806</t>
+          <t>381105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>424691</t>
+          <t>422528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107653</t>
+          <t>108147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130234</t>
+          <t>130210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>500671</t>
+          <t>499117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>545941</t>
+          <t>547609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116854</t>
+          <t>119017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157739</t>
+          <t>160440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>58655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162406</t>
+          <t>160738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207676</t>
+          <t>209230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>869866</t>
+          <t>869423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>931486</t>
+          <t>931524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>505815</t>
+          <t>508170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>554093</t>
+          <t>554842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1397961</t>
+          <t>1396244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1474442</t>
+          <t>1472504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306848</t>
+          <t>306810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368468</t>
+          <t>368911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>159443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208470</t>
+          <t>206115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>478178</t>
+          <t>480116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554659</t>
+          <t>556376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>234437</t>
+          <t>233429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267949</t>
+          <t>268069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>431794</t>
+          <t>431553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>468255</t>
+          <t>470703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>676528</t>
+          <t>678029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>729652</t>
+          <t>726824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82606</t>
+          <t>82486</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116118</t>
+          <t>117126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>97054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135963</t>
+          <t>136204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188660</t>
+          <t>191488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241784</t>
+          <t>240283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>160576</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>195527</t>
+          <t>193561</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>847938</t>
+          <t>844938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>910027</t>
+          <t>909821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1019977</t>
+          <t>1021379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1096488</t>
+          <t>1092979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101836</t>
+          <t>103802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135777</t>
+          <t>136787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338733</t>
+          <t>338939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>400822</t>
+          <t>403822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449635</t>
+          <t>453144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526146</t>
+          <t>524744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2242352</t>
+          <t>2247668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2352920</t>
+          <t>2348736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2387928</t>
+          <t>2387729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2491068</t>
+          <t>2486086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4661021</t>
+          <t>4663061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4807410</t>
+          <t>4817526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>911203</t>
+          <t>915387</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1021771</t>
+          <t>1016455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>883930</t>
+          <t>888912</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>987070</t>
+          <t>987269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1831711</t>
+          <t>1821595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1978100</t>
+          <t>1976060</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272711</t>
+          <t>274280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>313118</t>
+          <t>315605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199919</t>
+          <t>198750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234814</t>
+          <t>233454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>485034</t>
+          <t>485383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>540019</t>
+          <t>537559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122166</t>
+          <t>119679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162573</t>
+          <t>161004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75262</t>
+          <t>76622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110157</t>
+          <t>111326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205341</t>
+          <t>207801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260326</t>
+          <t>259977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261289</t>
+          <t>259508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301140</t>
+          <t>301401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>227255</t>
+          <t>228697</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262791</t>
+          <t>260423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>502275</t>
+          <t>499780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>555973</t>
+          <t>553185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114438</t>
+          <t>114177</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154289</t>
+          <t>156070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71557</t>
+          <t>73925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107093</t>
+          <t>105651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193954</t>
+          <t>196742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247652</t>
+          <t>250147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>399021</t>
+          <t>400850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>447667</t>
+          <t>448535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>173701</t>
+          <t>172402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202709</t>
+          <t>202482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>585348</t>
+          <t>586456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>639037</t>
+          <t>642347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174262</t>
+          <t>173394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222908</t>
+          <t>221079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>56711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>86791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>238775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295774</t>
+          <t>294666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>768666</t>
+          <t>770563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>833122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>584090</t>
+          <t>583511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>627652</t>
+          <t>629235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1374194</t>
+          <t>1369167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1448636</t>
+          <t>1446043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308782</t>
+          <t>310179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>374635</t>
+          <t>372738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133073</t>
+          <t>131490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176635</t>
+          <t>177214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>455390</t>
+          <t>457983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>529832</t>
+          <t>534859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>342785</t>
+          <t>344718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>383055</t>
+          <t>384529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>555088</t>
+          <t>555464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>602690</t>
+          <t>602651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>912990</t>
+          <t>913146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>974894</t>
+          <t>975811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117345</t>
+          <t>115871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157615</t>
+          <t>155682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149538</t>
+          <t>149577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197140</t>
+          <t>196764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277734</t>
+          <t>276817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339638</t>
+          <t>339482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145858</t>
+          <t>147044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177175</t>
+          <t>178739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>777702</t>
+          <t>775251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>832763</t>
+          <t>835953</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>935052</t>
+          <t>932582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1001783</t>
+          <t>999957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87816</t>
+          <t>86252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119133</t>
+          <t>117947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266356</t>
+          <t>263166</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>321417</t>
+          <t>323868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>362326</t>
+          <t>364152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>429057</t>
+          <t>431527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2273941</t>
+          <t>2279613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2387889</t>
+          <t>2384811</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2596197</t>
+          <t>2594035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2700480</t>
+          <t>2699864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4902803</t>
+          <t>4897257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5056820</t>
+          <t>5049647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>993594</t>
+          <t>996672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1107542</t>
+          <t>1101870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>815210</t>
+          <t>815826</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>919493</t>
+          <t>921655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1840352</t>
+          <t>1847525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1994369</t>
+          <t>1999915</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321259</t>
+          <t>322118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>356903</t>
+          <t>356483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>260348</t>
+          <t>258880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>287697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>590017</t>
+          <t>590976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>636139</t>
+          <t>635660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>71744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51986</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>82565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133533</t>
+          <t>134012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179655</t>
+          <t>178696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270213</t>
+          <t>271249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303873</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>276015</t>
+          <t>279292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308232</t>
+          <t>310254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>559836</t>
+          <t>557975</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>605097</t>
+          <t>604527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>69431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102885</t>
+          <t>101849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58487</t>
+          <t>56465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90704</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134720</t>
+          <t>135290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179981</t>
+          <t>181842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>434083</t>
+          <t>433603</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>466674</t>
+          <t>464117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132042</t>
+          <t>131827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150284</t>
+          <t>150049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>573742</t>
+          <t>575577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>609639</t>
+          <t>610674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>56831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86865</t>
+          <t>87345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73893</t>
+          <t>72858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>107955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>906114</t>
+          <t>906948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>956882</t>
+          <t>958199</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>681973</t>
+          <t>683668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>722480</t>
+          <t>720916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1600038</t>
+          <t>1601907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1666387</t>
+          <t>1668805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179635</t>
+          <t>178318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230403</t>
+          <t>229569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>98356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137299</t>
+          <t>135604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289402</t>
+          <t>286984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355751</t>
+          <t>353882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>492302</t>
+          <t>493385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>530005</t>
+          <t>531564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>618802</t>
+          <t>617694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>655283</t>
+          <t>653716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1123581</t>
+          <t>1123918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1175800</t>
+          <t>1175219</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84376</t>
+          <t>82817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122079</t>
+          <t>120996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76064</t>
+          <t>77631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112545</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169928</t>
+          <t>170509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222147</t>
+          <t>221810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210466</t>
+          <t>212432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238591</t>
+          <t>239834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>884547</t>
+          <t>884091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>931765</t>
+          <t>933005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1110703</t>
+          <t>1110423</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1163815</t>
+          <t>1165016</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75728</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142685</t>
+          <t>141445</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189903</t>
+          <t>190359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196829</t>
+          <t>195628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249941</t>
+          <t>250221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2702866</t>
+          <t>2704185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2793247</t>
+          <t>2791141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2915562</t>
+          <t>2921401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3004084</t>
+          <t>3009090</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5651621</t>
+          <t>5643260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5775713</t>
+          <t>5773439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>566117</t>
+          <t>568223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656498</t>
+          <t>655179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>491734</t>
+          <t>486728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>580256</t>
+          <t>574417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1079469</t>
+          <t>1081743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1203561</t>
+          <t>1211922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>289112</t>
+          <t>321899</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266824</t>
+          <t>295963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312572</t>
+          <t>344642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>239022</t>
+          <t>265258</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>221106</t>
+          <t>242768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256406</t>
+          <t>283931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>528134</t>
+          <t>587157</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>496873</t>
+          <t>556921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>556838</t>
+          <t>620508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>207170</t>
+          <t>219707</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183710</t>
+          <t>196964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229458</t>
+          <t>245643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>204381</t>
+          <t>218068</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186997</t>
+          <t>199395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>222297</t>
+          <t>240558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>411551</t>
+          <t>437775</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382847</t>
+          <t>404424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442812</t>
+          <t>468011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>496282</t>
+          <t>541606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>496282</t>
+          <t>541606</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>496282</t>
+          <t>541606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>443403</t>
+          <t>483326</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>443403</t>
+          <t>483326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>443403</t>
+          <t>483326</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>1024932</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>1024932</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>1024932</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>287648</t>
+          <t>314693</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>265104</t>
+          <t>293198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307439</t>
+          <t>335788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>243220</t>
+          <t>267249</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>225881</t>
+          <t>248839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259355</t>
+          <t>284563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>530867</t>
+          <t>581942</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501882</t>
+          <t>553920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>557149</t>
+          <t>612470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>159676</t>
+          <t>163501</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139885</t>
+          <t>142406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182220</t>
+          <t>184996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>134002</t>
+          <t>149880</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>132566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151341</t>
+          <t>168290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>293679</t>
+          <t>313381</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267397</t>
+          <t>282853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322664</t>
+          <t>341403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>447324</t>
+          <t>478194</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>447324</t>
+          <t>478194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>447324</t>
+          <t>478194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377222</t>
+          <t>417129</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377222</t>
+          <t>417129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377222</t>
+          <t>417129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>824546</t>
+          <t>895323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>824546</t>
+          <t>895323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>824546</t>
+          <t>895323</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>271813</t>
+          <t>301406</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106364</t>
+          <t>278398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>437978</t>
+          <t>322277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111031</t>
+          <t>122540</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101176</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119753</t>
+          <t>132482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>382845</t>
+          <t>423945</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155507</t>
+          <t>398654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>556159</t>
+          <t>445507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>389772</t>
+          <t>162291</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>223607</t>
+          <t>141420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555221</t>
+          <t>185299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>61824</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>51882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>74344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>442745</t>
+          <t>224116</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269431</t>
+          <t>202554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670083</t>
+          <t>249407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>661585</t>
+          <t>463697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>661585</t>
+          <t>463697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>661585</t>
+          <t>463697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164005</t>
+          <t>184364</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164005</t>
+          <t>184364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164005</t>
+          <t>184364</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825590</t>
+          <t>648061</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825590</t>
+          <t>648061</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825590</t>
+          <t>648061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>668244</t>
+          <t>742478</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>636498</t>
+          <t>708058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>704632</t>
+          <t>774779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>480489</t>
+          <t>547749</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>456363</t>
+          <t>522670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>502582</t>
+          <t>573518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1148733</t>
+          <t>1290226</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1110272</t>
+          <t>1246566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1188960</t>
+          <t>1330866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>378488</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>319648</t>
+          <t>346187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387782</t>
+          <t>412908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>278372</t>
+          <t>297240</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256279</t>
+          <t>271471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302498</t>
+          <t>322319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>634407</t>
+          <t>675729</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594180</t>
+          <t>635089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672868</t>
+          <t>719389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1024280</t>
+          <t>1120966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1024280</t>
+          <t>1120966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1024280</t>
+          <t>1120966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>758861</t>
+          <t>844989</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>758861</t>
+          <t>844989</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>758861</t>
+          <t>844989</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1783140</t>
+          <t>1965955</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1783140</t>
+          <t>1965955</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1783140</t>
+          <t>1965955</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>321933</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300755</t>
+          <t>363497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342785</t>
+          <t>412984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>514451</t>
+          <t>587286</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>398388</t>
+          <t>564453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>583917</t>
+          <t>607994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>836383</t>
+          <t>975318</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674833</t>
+          <t>945874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>906582</t>
+          <t>1012928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>142755</t>
+          <t>167770</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121903</t>
+          <t>142818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163933</t>
+          <t>192305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>310480</t>
+          <t>225441</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241014</t>
+          <t>204733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>426543</t>
+          <t>248274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>453236</t>
+          <t>393211</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383037</t>
+          <t>355601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>614786</t>
+          <t>422655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>464688</t>
+          <t>555802</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464688</t>
+          <t>555802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>464688</t>
+          <t>555802</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>824931</t>
+          <t>812727</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>824931</t>
+          <t>812727</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>824931</t>
+          <t>812727</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1289619</t>
+          <t>1368529</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1289619</t>
+          <t>1368529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1289619</t>
+          <t>1368529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>107709</t>
+          <t>112948</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82477</t>
+          <t>88880</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133873</t>
+          <t>135947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>478682</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>450015</t>
+          <t>513176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>501633</t>
+          <t>569639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>586391</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>545151</t>
+          <t>614790</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>623968</t>
+          <t>690026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>130158</t>
+          <t>121574</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103994</t>
+          <t>98575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155390</t>
+          <t>145642</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>262727</t>
+          <t>283955</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239776</t>
+          <t>255848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>291394</t>
+          <t>312311</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>392885</t>
+          <t>405529</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>355308</t>
+          <t>369982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434125</t>
+          <t>445218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>237867</t>
+          <t>234522</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>237867</t>
+          <t>234522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>237867</t>
+          <t>234522</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>741409</t>
+          <t>825487</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>741409</t>
+          <t>825487</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>741409</t>
+          <t>825487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>979276</t>
+          <t>1060008</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>979276</t>
+          <t>1060008</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>979276</t>
+          <t>1060008</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1946458</t>
+          <t>2181456</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1386556</t>
+          <t>2121474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2120645</t>
+          <t>2245411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2066895</t>
+          <t>2331613</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1890062</t>
+          <t>2279286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2140009</t>
+          <t>2381587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4013353</t>
+          <t>4513069</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3416545</t>
+          <t>4421838</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4208066</t>
+          <t>4590841</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1385567</t>
+          <t>1213331</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1211380</t>
+          <t>1149376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1945469</t>
+          <t>1273313</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1242935</t>
+          <t>1236409</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1169821</t>
+          <t>1186435</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1419768</t>
+          <t>1288736</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2628502</t>
+          <t>2449741</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2433789</t>
+          <t>2371969</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3225310</t>
+          <t>2540972</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3332025</t>
+          <t>3394787</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3332025</t>
+          <t>3394787</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3332025</t>
+          <t>3394787</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3309830</t>
+          <t>3568022</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3309830</t>
+          <t>3568022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3309830</t>
+          <t>3568022</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6641855</t>
+          <t>6962810</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6641855</t>
+          <t>6962810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6641855</t>
+          <t>6962810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
